--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/second/CF_M04_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/second/CF_M04_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.5789</v>
       </c>
       <c r="D13" t="n">
+        <v>0.7213000000000001</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9665</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall display a Home screen with relevant business information for authenticated users.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -773,10 +777,6 @@
 of my business</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -807,10 +807,6 @@
           <t>The system shall allow delegated users to log in using their email or phone number.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -825,10 +821,6 @@
 phone number</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -859,10 +851,6 @@
           <t>The system shall allow users to view images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -876,10 +864,6 @@
           <t xml:space="preserve"> I want to be able to see images and videos associated with a review</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -915,9 +899,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>QR</t>
@@ -941,8 +922,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -973,14 +952,11 @@
           <t>If Cintia is active, the system must show a response suggestion automatically upon opening the response modal.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -994,14 +970,11 @@
           <t>If Cintia is active, the system must display a response suggestion.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1037,9 +1010,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1063,8 +1033,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,14 +1063,11 @@
           <t>The system must display images and videos associated with a review under the review text.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1116,14 +1081,11 @@
           <t>The system must display the images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1154,14 +1116,11 @@
           <t>The system must show loading and error states when necessary.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1175,14 +1134,11 @@
           <t>The system must display loading and error statuses when necessary.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1213,14 +1169,11 @@
           <t>Clicking an image or video must display it in full screen.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1234,14 +1187,11 @@
           <t>When clicking an image or video, it must be displayed in full screen.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1272,14 +1222,11 @@
           <t>Images must be navigable via horizontal scroll.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1293,14 +1240,11 @@
           <t>The images must be navigable via horizontal scrolling.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1336,9 +1280,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1362,8 +1303,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1394,14 +1333,11 @@
           <t>The Home screen must show several independent informative widgets.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1415,14 +1351,11 @@
           <t>The Home screen must display several independent informative widgets.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1458,9 +1391,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1484,8 +1414,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1521,9 +1449,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1547,8 +1472,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1579,14 +1502,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1600,14 +1520,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1638,14 +1555,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1659,14 +1573,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1697,14 +1608,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1718,14 +1626,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1756,14 +1661,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1777,14 +1679,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1815,14 +1714,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1836,14 +1732,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1874,14 +1767,11 @@
           <t>The system must detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1895,14 +1785,11 @@
           <t>The system must detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1933,14 +1820,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1954,14 +1838,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1992,14 +1873,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2013,14 +1891,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
